--- a/db/templates/delivery_tunisia.xlsx
+++ b/db/templates/delivery_tunisia.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>{{organization.logo}}</t>
   </si>
@@ -41,7 +41,7 @@
     <t>{{client.name}}</t>
   </si>
   <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
+    <t>{{client.addressLine}}</t>
   </si>
   <si>
     <t>{{client.postalCode}} {{client.city}}</t>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>Customer street and house number, or the single-line address when there is no street</t>
   </si>
   <si>
     <t>{{client.email}}</t>
@@ -1080,84 +1083,84 @@
     </row>
     <row r="27">
       <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
         <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
         <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
         <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
         <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" t="s">
         <v>83</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35">
+      <c r="B35" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="s">
+      <c r="C35" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="A36" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
         <v>87</v>
@@ -1165,7 +1168,7 @@
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
         <v>88</v>
@@ -1173,7 +1176,7 @@
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
         <v>89</v>
@@ -1181,61 +1184,69 @@
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="s">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="s">
+      <c r="A42" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43">
+      <c r="B43" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="s">
+      <c r="C43" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="s">
+      <c r="A44" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
         <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
         <v>99</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47">
+      <c r="B47" t="s">
         <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
 </worksheet>
 </file>